--- a/ascend_test_suite/v0.26.0rc1-pub/vLLM_model_list.xlsx
+++ b/ascend_test_suite/v0.26.0rc1-pub/vLLM_model_list.xlsx
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" sd-vllm-ascend:v0.26.0rc1-pub sed -i 's/--port 8023/--port $PORT/' /workspace/cmd/serve.sh; sed -i 's/--block-size 64/--block-size 128/' /workspace/cmd/serve.sh; /workspace/cmd/serve.sh -tp 8</t>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" xcoresigma-registry.cn-beijing.cr.aliyuncs.com/docker/sd-vllm-ascend:v0.26.0rc1-pub-v1 sed -i 's/--port 8023/--port $PORT/' /workspace/cmd/serve.sh; sed -i 's/--block-size 64/--block-size 128/' /workspace/cmd/serve.sh; /workspace/cmd/serve.sh -tp 8</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
